--- a/wayforge/docs/M1_Feature_Plan_Template.xlsx
+++ b/wayforge/docs/M1_Feature_Plan_Template.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30502"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_3BA7DD8A597207DFC2D0979FAFB8242ED684E64B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{030058C5-BDE1-4FD6-92A8-195234B6B8A4}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Joel\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F68C21DC-C4C3-4014-AD3C-3DADC8DED68E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="M1 Feature Plan" sheetId="1" r:id="rId1"/>
@@ -32,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="162">
   <si>
     <t>MILESTONE 1 FEATURE PLAN - TEAM PLANNING SHEET [For Parminder Teams]</t>
   </si>
@@ -472,12 +477,63 @@
   <si>
     <t>Fxx = what can the user do?   |   Txx = what do we need to engineer?   |   Jira = what work must we do?   |   M1 Contract = what have we promised?   |   TI-xx = did we go beyond the normal expectation?</t>
   </si>
+  <si>
+    <t>able to save places for future uses</t>
+  </si>
+  <si>
+    <t>User can get walking directions to destination based on current location</t>
+  </si>
+  <si>
+    <t>Route to Site</t>
+  </si>
+  <si>
+    <t>Step-free Route</t>
+  </si>
+  <si>
+    <t>User can get walking directions (that does not involve stairs) to destination based on current location</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If user has walking disabilities </t>
+  </si>
+  <si>
+    <t>User will know how to get to destination</t>
+  </si>
+  <si>
+    <t>Map viewability 2D/3D</t>
+  </si>
+  <si>
+    <t>View the map in 2D/3D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User can see where they are in a building </t>
+  </si>
+  <si>
+    <t>User can save the route for future uses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Convenience sake if the destination is frequent </t>
+  </si>
+  <si>
+    <t>Lost?</t>
+  </si>
+  <si>
+    <t>User is able to update their current location</t>
+  </si>
+  <si>
+    <t>If lost, the app will reroute for the user</t>
+  </si>
+  <si>
+    <t>On the right path</t>
+  </si>
+  <si>
+    <t>User can update their current location</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -537,32 +593,38 @@
       <b/>
       <sz val="16"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <i/>
       <sz val="9"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="9">
@@ -729,82 +791,82 @@
     <xf numFmtId="0" fontId="12" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1108,9 +1170,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="C1:K48"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="2.42578125" customWidth="1"/>
+    <col min="1" max="2" width="2.453125" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="32" customWidth="1"/>
     <col min="5" max="5" width="56" customWidth="1"/>
@@ -1121,19 +1183,19 @@
     <col min="11" max="11" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:11">
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-    </row>
-    <row r="2" spans="3:11" ht="26.1" customHeight="1">
-      <c r="C2" s="6" t="s">
+    <row r="1" spans="3:11" x14ac:dyDescent="0.35">
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+    </row>
+    <row r="2" spans="3:11" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C2" s="24" t="s">
         <v>0</v>
       </c>
       <c r="D2" s="19"/>
@@ -1145,32 +1207,32 @@
       <c r="J2" s="19"/>
       <c r="K2" s="19"/>
     </row>
-    <row r="3" spans="3:11" ht="20.100000000000001" customHeight="1">
-      <c r="C3" s="9" t="s">
+    <row r="3" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C3" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="20"/>
-      <c r="I3" s="20"/>
-      <c r="J3" s="20"/>
-      <c r="K3" s="21"/>
-    </row>
-    <row r="4" spans="3:11">
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
-    </row>
-    <row r="5" spans="3:11" ht="189.95" customHeight="1">
-      <c r="C5" s="7" t="s">
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
+      <c r="J3" s="26"/>
+      <c r="K3" s="27"/>
+    </row>
+    <row r="4" spans="3:11" x14ac:dyDescent="0.35">
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+    </row>
+    <row r="5" spans="3:11" ht="123" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C5" s="18" t="s">
         <v>2</v>
       </c>
       <c r="D5" s="19"/>
@@ -1182,573 +1244,618 @@
       <c r="J5" s="19"/>
       <c r="K5" s="19"/>
     </row>
-    <row r="6" spans="3:11">
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="18"/>
-      <c r="K6" s="18"/>
-    </row>
-    <row r="7" spans="3:11">
-      <c r="C7" s="22" t="s">
+    <row r="6" spans="3:11" x14ac:dyDescent="0.35">
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+    </row>
+    <row r="7" spans="3:11" x14ac:dyDescent="0.35">
+      <c r="C7" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="D7" s="23"/>
-      <c r="E7" s="23"/>
-      <c r="F7" s="23"/>
-      <c r="G7" s="23"/>
-      <c r="H7" s="23"/>
-      <c r="I7" s="23"/>
-      <c r="J7" s="23"/>
-      <c r="K7" s="24"/>
-    </row>
-    <row r="8" spans="3:11" ht="33.950000000000003" customHeight="1">
-      <c r="C8" s="25" t="s">
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="15"/>
+    </row>
+    <row r="8" spans="3:11" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C8" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="26" t="s">
+      <c r="D8" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="E8" s="26" t="s">
+      <c r="E8" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="F8" s="26" t="s">
+      <c r="F8" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="G8" s="25" t="s">
+      <c r="G8" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="H8" s="26" t="s">
+      <c r="H8" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="I8" s="26" t="s">
+      <c r="I8" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="J8" s="18"/>
-      <c r="K8" s="26" t="s">
+      <c r="J8" s="6"/>
+      <c r="K8" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="3:11">
-      <c r="C9" s="18"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="18"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="18"/>
-      <c r="K9" s="18"/>
-    </row>
-    <row r="10" spans="3:11" ht="32.1" customHeight="1">
-      <c r="C10" s="27" t="s">
+    <row r="9" spans="3:11" ht="19" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+    </row>
+    <row r="10" spans="3:11" ht="74.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C10" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="27" t="s">
+      <c r="D10" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E10" s="27" t="s">
+      <c r="E10" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F10" s="27" t="s">
+      <c r="F10" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="G10" s="27" t="s">
+      <c r="G10" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H10" s="27" t="s">
+      <c r="H10" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="I10" s="27" t="s">
+      <c r="I10" s="9" t="s">
         <v>18</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="K10" s="27" t="s">
+      <c r="K10" s="9" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="3:11" ht="30" customHeight="1">
-      <c r="C11" s="28" t="s">
+    <row r="11" spans="3:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C11" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="29"/>
-      <c r="E11" s="30"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="31"/>
-      <c r="H11" s="30"/>
-      <c r="I11" s="30"/>
+      <c r="D11" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="G11" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12"/>
       <c r="J11" s="5"/>
-      <c r="K11" s="30"/>
-    </row>
-    <row r="12" spans="3:11" ht="30" customHeight="1">
-      <c r="C12" s="28" t="s">
+      <c r="K11" s="12"/>
+    </row>
+    <row r="12" spans="3:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C12" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="29"/>
-      <c r="E12" s="30"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="31"/>
-      <c r="H12" s="30"/>
-      <c r="I12" s="30"/>
+      <c r="D12" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="G12" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
       <c r="J12" s="5"/>
-      <c r="K12" s="30"/>
-    </row>
-    <row r="13" spans="3:11" ht="30" customHeight="1">
-      <c r="C13" s="28" t="s">
+      <c r="K12" s="12"/>
+    </row>
+    <row r="13" spans="3:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C13" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="D13" s="29"/>
-      <c r="E13" s="30"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="31"/>
-      <c r="H13" s="30"/>
-      <c r="I13" s="30"/>
+      <c r="D13" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="G13" s="13"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="12"/>
       <c r="J13" s="5"/>
-      <c r="K13" s="30"/>
-    </row>
-    <row r="14" spans="3:11" ht="30" customHeight="1">
-      <c r="C14" s="28" t="s">
+      <c r="K13" s="12"/>
+    </row>
+    <row r="14" spans="3:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C14" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="29"/>
-      <c r="E14" s="30"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="31"/>
-      <c r="H14" s="30"/>
-      <c r="I14" s="30"/>
+      <c r="D14" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="G14" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12"/>
       <c r="J14" s="5"/>
-      <c r="K14" s="30"/>
-    </row>
-    <row r="15" spans="3:11" ht="30" customHeight="1">
-      <c r="C15" s="28" t="s">
+      <c r="K14" s="12"/>
+    </row>
+    <row r="15" spans="3:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C15" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D15" s="29"/>
-      <c r="E15" s="30"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="30"/>
-      <c r="I15" s="30"/>
+      <c r="D15" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="G15" s="13"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="12"/>
       <c r="J15" s="5"/>
-      <c r="K15" s="30"/>
-    </row>
-    <row r="16" spans="3:11" ht="30" customHeight="1">
-      <c r="C16" s="28" t="s">
+      <c r="K15" s="12"/>
+    </row>
+    <row r="16" spans="3:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C16" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="29"/>
-      <c r="E16" s="30"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="31"/>
-      <c r="H16" s="30"/>
-      <c r="I16" s="30"/>
+      <c r="D16" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="F16" s="12"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="12"/>
       <c r="J16" s="5"/>
-      <c r="K16" s="30"/>
-    </row>
-    <row r="17" spans="3:11" ht="30" customHeight="1">
-      <c r="C17" s="28" t="s">
+      <c r="K16" s="12"/>
+    </row>
+    <row r="17" spans="3:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C17" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D17" s="29"/>
-      <c r="E17" s="30"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="31"/>
-      <c r="H17" s="30"/>
-      <c r="I17" s="30"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="12"/>
       <c r="J17" s="5"/>
-      <c r="K17" s="30"/>
-    </row>
-    <row r="18" spans="3:11" ht="30" customHeight="1">
-      <c r="C18" s="28" t="s">
+      <c r="K17" s="12"/>
+    </row>
+    <row r="18" spans="3:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C18" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="29"/>
-      <c r="E18" s="30"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="31"/>
-      <c r="H18" s="30"/>
-      <c r="I18" s="30"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
       <c r="J18" s="5"/>
-      <c r="K18" s="30"/>
-    </row>
-    <row r="19" spans="3:11" ht="30" customHeight="1">
-      <c r="C19" s="28" t="s">
+      <c r="K18" s="12"/>
+    </row>
+    <row r="19" spans="3:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C19" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D19" s="29"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="31"/>
-      <c r="H19" s="30"/>
-      <c r="I19" s="30"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="12"/>
       <c r="J19" s="5"/>
-      <c r="K19" s="30"/>
-    </row>
-    <row r="20" spans="3:11" ht="30" customHeight="1">
-      <c r="C20" s="28" t="s">
+      <c r="K19" s="12"/>
+    </row>
+    <row r="20" spans="3:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C20" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="D20" s="29"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="31"/>
-      <c r="H20" s="30"/>
-      <c r="I20" s="30"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="12"/>
       <c r="J20" s="5"/>
-      <c r="K20" s="30"/>
-    </row>
-    <row r="21" spans="3:11" ht="30" customHeight="1">
-      <c r="C21" s="28" t="s">
+      <c r="K20" s="12"/>
+    </row>
+    <row r="21" spans="3:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C21" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="29"/>
-      <c r="E21" s="30"/>
-      <c r="F21" s="30"/>
-      <c r="G21" s="31"/>
-      <c r="H21" s="30"/>
-      <c r="I21" s="30"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="12"/>
       <c r="J21" s="5"/>
-      <c r="K21" s="30"/>
-    </row>
-    <row r="22" spans="3:11" ht="30" customHeight="1">
-      <c r="C22" s="28" t="s">
+      <c r="K21" s="12"/>
+    </row>
+    <row r="22" spans="3:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C22" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="D22" s="29"/>
-      <c r="E22" s="30"/>
-      <c r="F22" s="30"/>
-      <c r="G22" s="31"/>
-      <c r="H22" s="30"/>
-      <c r="I22" s="30"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="12"/>
+      <c r="I22" s="12"/>
       <c r="J22" s="5"/>
-      <c r="K22" s="30"/>
-    </row>
-    <row r="23" spans="3:11" ht="30" customHeight="1">
-      <c r="C23" s="28" t="s">
+      <c r="K22" s="12"/>
+    </row>
+    <row r="23" spans="3:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C23" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="29"/>
-      <c r="E23" s="30"/>
-      <c r="F23" s="30"/>
-      <c r="G23" s="31"/>
-      <c r="H23" s="30"/>
-      <c r="I23" s="30"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="12"/>
       <c r="J23" s="5"/>
-      <c r="K23" s="30"/>
-    </row>
-    <row r="24" spans="3:11" ht="30" customHeight="1">
-      <c r="C24" s="28" t="s">
+      <c r="K23" s="12"/>
+    </row>
+    <row r="24" spans="3:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C24" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="D24" s="29"/>
-      <c r="E24" s="30"/>
-      <c r="F24" s="30"/>
-      <c r="G24" s="31"/>
-      <c r="H24" s="30"/>
-      <c r="I24" s="30"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="12"/>
       <c r="J24" s="5"/>
-      <c r="K24" s="30"/>
-    </row>
-    <row r="25" spans="3:11" ht="30" customHeight="1">
-      <c r="C25" s="28" t="s">
+      <c r="K24" s="12"/>
+    </row>
+    <row r="25" spans="3:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C25" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="D25" s="29"/>
-      <c r="E25" s="30"/>
-      <c r="F25" s="30"/>
-      <c r="G25" s="31"/>
-      <c r="H25" s="30"/>
-      <c r="I25" s="30"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="13"/>
+      <c r="H25" s="12"/>
+      <c r="I25" s="12"/>
       <c r="J25" s="5"/>
-      <c r="K25" s="30"/>
-    </row>
-    <row r="26" spans="3:11">
-      <c r="C26" s="18"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="18"/>
-      <c r="H26" s="18"/>
-      <c r="I26" s="18"/>
-      <c r="J26" s="18"/>
-      <c r="K26" s="18"/>
-    </row>
-    <row r="27" spans="3:11">
-      <c r="C27" s="32" t="s">
+      <c r="K25" s="12"/>
+    </row>
+    <row r="26" spans="3:11" x14ac:dyDescent="0.35">
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="6"/>
+      <c r="I26" s="6"/>
+      <c r="J26" s="6"/>
+      <c r="K26" s="6"/>
+    </row>
+    <row r="27" spans="3:11" x14ac:dyDescent="0.35">
+      <c r="C27" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="23"/>
-      <c r="H27" s="23"/>
-      <c r="I27" s="23"/>
-      <c r="J27" s="23"/>
-      <c r="K27" s="24"/>
-    </row>
-    <row r="28" spans="3:11" ht="26.1" customHeight="1">
-      <c r="C28" s="33" t="s">
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="17"/>
+      <c r="I27" s="17"/>
+      <c r="J27" s="17"/>
+      <c r="K27" s="15"/>
+    </row>
+    <row r="28" spans="3:11" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C28" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="D28" s="24"/>
-      <c r="E28" s="34" t="s">
+      <c r="D28" s="15"/>
+      <c r="E28" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="F28" s="23"/>
-      <c r="G28" s="23"/>
-      <c r="H28" s="23"/>
-      <c r="I28" s="23"/>
-      <c r="J28" s="23"/>
-      <c r="K28" s="24"/>
-    </row>
-    <row r="29" spans="3:11" ht="26.1" customHeight="1">
-      <c r="C29" s="33" t="s">
+      <c r="F28" s="17"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="17"/>
+      <c r="I28" s="17"/>
+      <c r="J28" s="17"/>
+      <c r="K28" s="15"/>
+    </row>
+    <row r="29" spans="3:11" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C29" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="D29" s="24"/>
-      <c r="E29" s="34" t="s">
+      <c r="D29" s="15"/>
+      <c r="E29" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="F29" s="23"/>
-      <c r="G29" s="23"/>
-      <c r="H29" s="23"/>
-      <c r="I29" s="23"/>
-      <c r="J29" s="23"/>
-      <c r="K29" s="24"/>
-    </row>
-    <row r="30" spans="3:11" ht="26.1" customHeight="1">
-      <c r="C30" s="33" t="s">
+      <c r="F29" s="17"/>
+      <c r="G29" s="17"/>
+      <c r="H29" s="17"/>
+      <c r="I29" s="17"/>
+      <c r="J29" s="17"/>
+      <c r="K29" s="15"/>
+    </row>
+    <row r="30" spans="3:11" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C30" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="D30" s="24"/>
-      <c r="E30" s="34" t="s">
+      <c r="D30" s="15"/>
+      <c r="E30" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="F30" s="23"/>
-      <c r="G30" s="23"/>
-      <c r="H30" s="23"/>
-      <c r="I30" s="23"/>
-      <c r="J30" s="23"/>
-      <c r="K30" s="24"/>
-    </row>
-    <row r="31" spans="3:11" ht="26.1" customHeight="1">
-      <c r="C31" s="33" t="s">
+      <c r="F30" s="17"/>
+      <c r="G30" s="17"/>
+      <c r="H30" s="17"/>
+      <c r="I30" s="17"/>
+      <c r="J30" s="17"/>
+      <c r="K30" s="15"/>
+    </row>
+    <row r="31" spans="3:11" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C31" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="24"/>
-      <c r="E31" s="34" t="s">
+      <c r="D31" s="15"/>
+      <c r="E31" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="F31" s="23"/>
-      <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
-      <c r="I31" s="23"/>
-      <c r="J31" s="23"/>
-      <c r="K31" s="24"/>
-    </row>
-    <row r="32" spans="3:11" ht="26.1" customHeight="1">
-      <c r="C32" s="33" t="s">
+      <c r="F31" s="17"/>
+      <c r="G31" s="17"/>
+      <c r="H31" s="17"/>
+      <c r="I31" s="17"/>
+      <c r="J31" s="17"/>
+      <c r="K31" s="15"/>
+    </row>
+    <row r="32" spans="3:11" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C32" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="D32" s="24"/>
-      <c r="E32" s="34" t="s">
+      <c r="D32" s="15"/>
+      <c r="E32" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="F32" s="23"/>
-      <c r="G32" s="23"/>
-      <c r="H32" s="23"/>
-      <c r="I32" s="23"/>
-      <c r="J32" s="23"/>
-      <c r="K32" s="24"/>
-    </row>
-    <row r="33" spans="3:11" ht="26.1" customHeight="1">
-      <c r="C33" s="8" t="s">
+      <c r="F32" s="17"/>
+      <c r="G32" s="17"/>
+      <c r="H32" s="17"/>
+      <c r="I32" s="17"/>
+      <c r="J32" s="17"/>
+      <c r="K32" s="15"/>
+    </row>
+    <row r="33" spans="3:11" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C33" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="D33" s="24"/>
-      <c r="E33" s="10" t="s">
+      <c r="D33" s="15"/>
+      <c r="E33" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="F33" s="23"/>
-      <c r="G33" s="23"/>
-      <c r="H33" s="23"/>
-      <c r="I33" s="23"/>
-      <c r="J33" s="23"/>
-      <c r="K33" s="24"/>
-    </row>
-    <row r="34" spans="3:11">
-      <c r="C34" s="18"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="18"/>
-      <c r="F34" s="18"/>
-      <c r="G34" s="18"/>
-      <c r="H34" s="18"/>
-      <c r="I34" s="18"/>
-      <c r="J34" s="18"/>
-      <c r="K34" s="18"/>
-    </row>
-    <row r="35" spans="3:11">
-      <c r="C35" s="18"/>
-      <c r="D35" s="18"/>
-      <c r="E35" s="18"/>
-      <c r="F35" s="18"/>
-      <c r="G35" s="18"/>
-      <c r="H35" s="18"/>
-      <c r="I35" s="18"/>
-      <c r="J35" s="18"/>
-      <c r="K35" s="18"/>
-    </row>
-    <row r="36" spans="3:11">
-      <c r="C36" s="18"/>
-      <c r="D36" s="18"/>
-      <c r="E36" s="18"/>
-      <c r="F36" s="18"/>
-      <c r="G36" s="18"/>
-      <c r="H36" s="18"/>
-      <c r="I36" s="18"/>
-      <c r="J36" s="18"/>
-      <c r="K36" s="18"/>
-    </row>
-    <row r="37" spans="3:11">
-      <c r="C37" s="18"/>
-      <c r="D37" s="18"/>
-      <c r="E37" s="18"/>
-      <c r="F37" s="18"/>
-      <c r="G37" s="18"/>
-      <c r="H37" s="18"/>
-      <c r="I37" s="18"/>
-      <c r="J37" s="18"/>
-      <c r="K37" s="18"/>
-    </row>
-    <row r="38" spans="3:11">
-      <c r="C38" s="18"/>
-      <c r="D38" s="18"/>
-      <c r="E38" s="18"/>
-      <c r="F38" s="18"/>
-      <c r="G38" s="18"/>
-      <c r="H38" s="18"/>
-      <c r="I38" s="18"/>
-      <c r="J38" s="18"/>
-      <c r="K38" s="18"/>
-    </row>
-    <row r="39" spans="3:11">
-      <c r="C39" s="18"/>
-      <c r="D39" s="18"/>
-      <c r="E39" s="18"/>
-      <c r="F39" s="18"/>
-      <c r="G39" s="18"/>
-      <c r="H39" s="18"/>
-      <c r="I39" s="18"/>
-      <c r="J39" s="18"/>
-      <c r="K39" s="18"/>
-    </row>
-    <row r="40" spans="3:11">
-      <c r="C40" s="18"/>
-      <c r="D40" s="18"/>
-      <c r="E40" s="18"/>
-      <c r="F40" s="18"/>
-      <c r="G40" s="18"/>
-      <c r="H40" s="18"/>
-      <c r="I40" s="18"/>
-      <c r="J40" s="18"/>
-      <c r="K40" s="18"/>
-    </row>
-    <row r="41" spans="3:11">
-      <c r="C41" s="18"/>
-      <c r="D41" s="18"/>
-      <c r="E41" s="18"/>
-      <c r="F41" s="18"/>
-      <c r="G41" s="18"/>
-      <c r="H41" s="18"/>
-      <c r="I41" s="18"/>
-      <c r="J41" s="18"/>
-      <c r="K41" s="18"/>
-    </row>
-    <row r="42" spans="3:11">
-      <c r="C42" s="18"/>
-      <c r="D42" s="18"/>
-      <c r="E42" s="18"/>
-      <c r="F42" s="18"/>
-      <c r="G42" s="18"/>
-      <c r="H42" s="18"/>
-      <c r="I42" s="18"/>
-      <c r="J42" s="18"/>
-      <c r="K42" s="18"/>
-    </row>
-    <row r="43" spans="3:11">
-      <c r="C43" s="18"/>
-      <c r="D43" s="18"/>
-      <c r="E43" s="18"/>
-      <c r="F43" s="18"/>
-      <c r="G43" s="18"/>
-      <c r="H43" s="18"/>
-      <c r="I43" s="18"/>
-      <c r="J43" s="18"/>
-      <c r="K43" s="18"/>
-    </row>
-    <row r="44" spans="3:11">
-      <c r="C44" s="18"/>
-      <c r="D44" s="18"/>
-      <c r="E44" s="18"/>
-      <c r="F44" s="18"/>
-      <c r="G44" s="18"/>
-      <c r="H44" s="18"/>
-      <c r="I44" s="18"/>
-      <c r="J44" s="18"/>
-      <c r="K44" s="18"/>
-    </row>
-    <row r="45" spans="3:11">
-      <c r="C45" s="18"/>
-      <c r="D45" s="18"/>
-      <c r="E45" s="18"/>
-      <c r="F45" s="18"/>
-      <c r="G45" s="18"/>
-      <c r="H45" s="18"/>
-      <c r="I45" s="18"/>
-      <c r="J45" s="18"/>
-      <c r="K45" s="18"/>
-    </row>
-    <row r="46" spans="3:11">
-      <c r="C46" s="18"/>
-      <c r="D46" s="18"/>
-      <c r="E46" s="18"/>
-      <c r="F46" s="18"/>
-      <c r="G46" s="18"/>
-      <c r="H46" s="18"/>
-      <c r="I46" s="18"/>
-      <c r="J46" s="18"/>
-      <c r="K46" s="18"/>
-    </row>
-    <row r="47" spans="3:11">
-      <c r="C47" s="18"/>
-      <c r="D47" s="18"/>
-      <c r="E47" s="18"/>
-      <c r="F47" s="18"/>
-      <c r="G47" s="18"/>
-      <c r="H47" s="18"/>
-      <c r="I47" s="18"/>
-      <c r="J47" s="18"/>
-      <c r="K47" s="18"/>
-    </row>
-    <row r="48" spans="3:11">
-      <c r="C48" s="18"/>
-      <c r="D48" s="18"/>
-      <c r="E48" s="18"/>
-      <c r="F48" s="18"/>
-      <c r="G48" s="18"/>
-      <c r="H48" s="18"/>
-      <c r="I48" s="18"/>
-      <c r="J48" s="18"/>
-      <c r="K48" s="18"/>
+      <c r="F33" s="17"/>
+      <c r="G33" s="17"/>
+      <c r="H33" s="17"/>
+      <c r="I33" s="17"/>
+      <c r="J33" s="17"/>
+      <c r="K33" s="15"/>
+    </row>
+    <row r="34" spans="3:11" x14ac:dyDescent="0.35">
+      <c r="C34" s="6"/>
+      <c r="D34" s="6"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="6"/>
+      <c r="I34" s="6"/>
+      <c r="J34" s="6"/>
+      <c r="K34" s="6"/>
+    </row>
+    <row r="35" spans="3:11" x14ac:dyDescent="0.35">
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="6"/>
+      <c r="G35" s="6"/>
+      <c r="H35" s="6"/>
+      <c r="I35" s="6"/>
+      <c r="J35" s="6"/>
+      <c r="K35" s="6"/>
+    </row>
+    <row r="36" spans="3:11" x14ac:dyDescent="0.35">
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
+      <c r="H36" s="6"/>
+      <c r="I36" s="6"/>
+      <c r="J36" s="6"/>
+      <c r="K36" s="6"/>
+    </row>
+    <row r="37" spans="3:11" x14ac:dyDescent="0.35">
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
+      <c r="H37" s="6"/>
+      <c r="I37" s="6"/>
+      <c r="J37" s="6"/>
+      <c r="K37" s="6"/>
+    </row>
+    <row r="38" spans="3:11" x14ac:dyDescent="0.35">
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
+      <c r="H38" s="6"/>
+      <c r="I38" s="6"/>
+      <c r="J38" s="6"/>
+      <c r="K38" s="6"/>
+    </row>
+    <row r="39" spans="3:11" x14ac:dyDescent="0.35">
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="6"/>
+      <c r="H39" s="6"/>
+      <c r="I39" s="6"/>
+      <c r="J39" s="6"/>
+      <c r="K39" s="6"/>
+    </row>
+    <row r="40" spans="3:11" x14ac:dyDescent="0.35">
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
+      <c r="H40" s="6"/>
+      <c r="I40" s="6"/>
+      <c r="J40" s="6"/>
+      <c r="K40" s="6"/>
+    </row>
+    <row r="41" spans="3:11" x14ac:dyDescent="0.35">
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="6"/>
+      <c r="H41" s="6"/>
+      <c r="I41" s="6"/>
+      <c r="J41" s="6"/>
+      <c r="K41" s="6"/>
+    </row>
+    <row r="42" spans="3:11" x14ac:dyDescent="0.35">
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="6"/>
+      <c r="H42" s="6"/>
+      <c r="I42" s="6"/>
+      <c r="J42" s="6"/>
+      <c r="K42" s="6"/>
+    </row>
+    <row r="43" spans="3:11" x14ac:dyDescent="0.35">
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="6"/>
+      <c r="H43" s="6"/>
+      <c r="I43" s="6"/>
+      <c r="J43" s="6"/>
+      <c r="K43" s="6"/>
+    </row>
+    <row r="44" spans="3:11" x14ac:dyDescent="0.35">
+      <c r="C44" s="6"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="6"/>
+      <c r="G44" s="6"/>
+      <c r="H44" s="6"/>
+      <c r="I44" s="6"/>
+      <c r="J44" s="6"/>
+      <c r="K44" s="6"/>
+    </row>
+    <row r="45" spans="3:11" x14ac:dyDescent="0.35">
+      <c r="C45" s="6"/>
+      <c r="D45" s="6"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="6"/>
+      <c r="G45" s="6"/>
+      <c r="H45" s="6"/>
+      <c r="I45" s="6"/>
+      <c r="J45" s="6"/>
+      <c r="K45" s="6"/>
+    </row>
+    <row r="46" spans="3:11" x14ac:dyDescent="0.35">
+      <c r="C46" s="6"/>
+      <c r="D46" s="6"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="6"/>
+      <c r="G46" s="6"/>
+      <c r="H46" s="6"/>
+      <c r="I46" s="6"/>
+      <c r="J46" s="6"/>
+      <c r="K46" s="6"/>
+    </row>
+    <row r="47" spans="3:11" x14ac:dyDescent="0.35">
+      <c r="C47" s="6"/>
+      <c r="D47" s="6"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="6"/>
+      <c r="G47" s="6"/>
+      <c r="H47" s="6"/>
+      <c r="I47" s="6"/>
+      <c r="J47" s="6"/>
+      <c r="K47" s="6"/>
+    </row>
+    <row r="48" spans="3:11" x14ac:dyDescent="0.35">
+      <c r="C48" s="6"/>
+      <c r="D48" s="6"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="6"/>
+      <c r="G48" s="6"/>
+      <c r="H48" s="6"/>
+      <c r="I48" s="6"/>
+      <c r="J48" s="6"/>
+      <c r="K48" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="C2:K2"/>
+    <mergeCell ref="E31:K31"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C3:K3"/>
     <mergeCell ref="C32:D32"/>
     <mergeCell ref="C27:K27"/>
     <mergeCell ref="C5:K5"/>
@@ -1761,11 +1868,6 @@
     <mergeCell ref="E33:K33"/>
     <mergeCell ref="C7:K7"/>
     <mergeCell ref="E28:K28"/>
-    <mergeCell ref="C2:K2"/>
-    <mergeCell ref="E31:K31"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C3:K3"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" errorTitle="Priority" error="Set MUST, SHOULD or COULD." sqref="G11:G25" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -1782,9 +1884,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="C2:G50"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="2.42578125" customWidth="1"/>
+    <col min="1" max="2" width="2.453125" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
     <col min="4" max="4" width="30" customWidth="1"/>
     <col min="5" max="5" width="64" customWidth="1"/>
@@ -1792,43 +1894,43 @@
     <col min="7" max="7" width="44" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:7" ht="26.1" customHeight="1">
-      <c r="C2" s="16" t="s">
+    <row r="2" spans="3:7" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C2" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-    </row>
-    <row r="3" spans="3:7">
-      <c r="C3" s="17" t="s">
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+    </row>
+    <row r="3" spans="3:7" x14ac:dyDescent="0.35">
+      <c r="C3" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="23"/>
-      <c r="G3" s="24"/>
-    </row>
-    <row r="5" spans="3:7" ht="26.1" customHeight="1">
-      <c r="C5" s="11" t="s">
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="15"/>
+    </row>
+    <row r="5" spans="3:7" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C5" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="D5" s="23"/>
-      <c r="E5" s="23"/>
-      <c r="F5" s="23"/>
-      <c r="G5" s="24"/>
-    </row>
-    <row r="7" spans="3:7">
-      <c r="C7" s="15" t="s">
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="15"/>
+    </row>
+    <row r="7" spans="3:7" x14ac:dyDescent="0.35">
+      <c r="C7" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="D7" s="23"/>
-      <c r="E7" s="23"/>
-      <c r="F7" s="23"/>
-      <c r="G7" s="24"/>
-    </row>
-    <row r="8" spans="3:7" ht="26.1" customHeight="1">
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="15"/>
+    </row>
+    <row r="8" spans="3:7" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C8" s="1" t="s">
         <v>47</v>
       </c>
@@ -1845,7 +1947,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="3:7" ht="36" customHeight="1">
+    <row r="9" spans="3:7" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C9" s="2" t="s">
         <v>50</v>
       </c>
@@ -1862,7 +1964,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="3:7" ht="24" customHeight="1">
+    <row r="10" spans="3:7" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C10" s="2" t="s">
         <v>50</v>
       </c>
@@ -1879,7 +1981,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="11" spans="3:7" ht="36" customHeight="1">
+    <row r="11" spans="3:7" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C11" s="2" t="s">
         <v>56</v>
       </c>
@@ -1896,7 +1998,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="12" spans="3:7" ht="36" customHeight="1">
+    <row r="12" spans="3:7" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C12" s="2" t="s">
         <v>56</v>
       </c>
@@ -1913,7 +2015,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="13" spans="3:7" ht="36" customHeight="1">
+    <row r="13" spans="3:7" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C13" s="2" t="s">
         <v>56</v>
       </c>
@@ -1930,7 +2032,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="3:7" ht="24" customHeight="1">
+    <row r="14" spans="3:7" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C14" s="2" t="s">
         <v>66</v>
       </c>
@@ -1947,7 +2049,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="15" spans="3:7" ht="24" customHeight="1">
+    <row r="15" spans="3:7" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C15" s="2" t="s">
         <v>66</v>
       </c>
@@ -1964,7 +2066,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="16" spans="3:7" ht="24" customHeight="1">
+    <row r="16" spans="3:7" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C16" s="2" t="s">
         <v>66</v>
       </c>
@@ -1981,7 +2083,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="17" spans="3:7" ht="24" customHeight="1">
+    <row r="17" spans="3:7" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C17" s="2" t="s">
         <v>77</v>
       </c>
@@ -1998,7 +2100,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="18" spans="3:7" ht="24" customHeight="1">
+    <row r="18" spans="3:7" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C18" s="2" t="s">
         <v>77</v>
       </c>
@@ -2015,7 +2117,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="19" spans="3:7" ht="24" customHeight="1">
+    <row r="19" spans="3:7" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C19" s="2" t="s">
         <v>84</v>
       </c>
@@ -2032,7 +2134,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="20" spans="3:7" ht="36" customHeight="1">
+    <row r="20" spans="3:7" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C20" s="2" t="s">
         <v>84</v>
       </c>
@@ -2049,7 +2151,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="21" spans="3:7" ht="24" customHeight="1">
+    <row r="21" spans="3:7" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C21" s="2" t="s">
         <v>84</v>
       </c>
@@ -2066,16 +2168,16 @@
         <v>93</v>
       </c>
     </row>
-    <row r="23" spans="3:7">
-      <c r="C23" s="15" t="s">
+    <row r="23" spans="3:7" x14ac:dyDescent="0.35">
+      <c r="C23" s="30" t="s">
         <v>94</v>
       </c>
-      <c r="D23" s="23"/>
-      <c r="E23" s="23"/>
-      <c r="F23" s="23"/>
-      <c r="G23" s="24"/>
-    </row>
-    <row r="24" spans="3:7" ht="26.1" customHeight="1">
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="15"/>
+    </row>
+    <row r="24" spans="3:7" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C24" s="1" t="s">
         <v>95</v>
       </c>
@@ -2085,23 +2187,23 @@
       <c r="E24" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
-    </row>
-    <row r="25" spans="3:7" ht="24" customHeight="1">
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+    </row>
+    <row r="25" spans="3:7" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C25" s="3" t="s">
         <v>98</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="E25" s="14" t="s">
+      <c r="E25" s="35" t="s">
         <v>100</v>
       </c>
-      <c r="F25" s="23"/>
-      <c r="G25" s="24"/>
-    </row>
-    <row r="26" spans="3:7" ht="36" customHeight="1">
+      <c r="F25" s="17"/>
+      <c r="G25" s="15"/>
+    </row>
+    <row r="26" spans="3:7" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C26" s="3" t="s">
         <v>101</v>
       </c>
@@ -2111,10 +2213,10 @@
       <c r="E26" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="F26" s="18"/>
-      <c r="G26" s="18"/>
-    </row>
-    <row r="27" spans="3:7" ht="24" customHeight="1">
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
+    </row>
+    <row r="27" spans="3:7" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C27" s="3" t="s">
         <v>104</v>
       </c>
@@ -2124,10 +2226,10 @@
       <c r="E27" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="F27" s="18"/>
-      <c r="G27" s="18"/>
-    </row>
-    <row r="28" spans="3:7" ht="36" customHeight="1">
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
+    </row>
+    <row r="28" spans="3:7" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C28" s="3" t="s">
         <v>107</v>
       </c>
@@ -2137,10 +2239,10 @@
       <c r="E28" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="F28" s="18"/>
-      <c r="G28" s="18"/>
-    </row>
-    <row r="29" spans="3:7" ht="36" customHeight="1">
+      <c r="F28" s="6"/>
+      <c r="G28" s="6"/>
+    </row>
+    <row r="29" spans="3:7" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C29" s="3" t="s">
         <v>110</v>
       </c>
@@ -2150,10 +2252,10 @@
       <c r="E29" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="F29" s="18"/>
-      <c r="G29" s="18"/>
-    </row>
-    <row r="30" spans="3:7" ht="24" customHeight="1">
+      <c r="F29" s="6"/>
+      <c r="G29" s="6"/>
+    </row>
+    <row r="30" spans="3:7" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C30" s="3" t="s">
         <v>113</v>
       </c>
@@ -2163,216 +2265,206 @@
       <c r="E30" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="F30" s="18"/>
-      <c r="G30" s="18"/>
-    </row>
-    <row r="32" spans="3:7">
-      <c r="C32" s="15" t="s">
+      <c r="F30" s="6"/>
+      <c r="G30" s="6"/>
+    </row>
+    <row r="32" spans="3:7" x14ac:dyDescent="0.35">
+      <c r="C32" s="30" t="s">
         <v>116</v>
       </c>
-      <c r="D32" s="23"/>
-      <c r="E32" s="23"/>
-      <c r="F32" s="23"/>
-      <c r="G32" s="24"/>
-    </row>
-    <row r="33" spans="3:7" ht="26.1" customHeight="1">
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17"/>
+      <c r="G32" s="15"/>
+    </row>
+    <row r="33" spans="3:7" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C33" s="1" t="s">
         <v>117</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="E33" s="18"/>
-      <c r="F33" s="18"/>
-      <c r="G33" s="18"/>
-    </row>
-    <row r="34" spans="3:7" ht="36" customHeight="1">
+      <c r="E33" s="6"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="6"/>
+    </row>
+    <row r="34" spans="3:7" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C34" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="D34" s="10" t="s">
+      <c r="D34" s="22" t="s">
         <v>120</v>
       </c>
-      <c r="E34" s="23"/>
-      <c r="F34" s="23"/>
-      <c r="G34" s="24"/>
-    </row>
-    <row r="35" spans="3:7" ht="36" customHeight="1">
+      <c r="E34" s="17"/>
+      <c r="F34" s="17"/>
+      <c r="G34" s="15"/>
+    </row>
+    <row r="35" spans="3:7" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C35" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="D35" s="10" t="s">
+      <c r="D35" s="22" t="s">
         <v>122</v>
       </c>
-      <c r="E35" s="23"/>
-      <c r="F35" s="23"/>
-      <c r="G35" s="24"/>
-    </row>
-    <row r="36" spans="3:7">
-      <c r="C36" s="18"/>
+      <c r="E35" s="17"/>
+      <c r="F35" s="17"/>
+      <c r="G35" s="15"/>
+    </row>
+    <row r="36" spans="3:7" x14ac:dyDescent="0.35">
+      <c r="C36" s="6"/>
       <c r="D36" s="19"/>
       <c r="E36" s="19"/>
       <c r="F36" s="19"/>
       <c r="G36" s="19"/>
     </row>
-    <row r="37" spans="3:7" ht="26.1" customHeight="1">
+    <row r="37" spans="3:7" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C37" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="E37" s="18"/>
-      <c r="F37" s="18"/>
-      <c r="G37" s="18"/>
-    </row>
-    <row r="38" spans="3:7" ht="32.1" customHeight="1">
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
+    </row>
+    <row r="38" spans="3:7" ht="32.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C38" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="D38" s="10" t="s">
+      <c r="D38" s="22" t="s">
         <v>126</v>
       </c>
-      <c r="E38" s="23"/>
-      <c r="F38" s="23"/>
-      <c r="G38" s="24"/>
-    </row>
-    <row r="39" spans="3:7" ht="48.95" customHeight="1">
+      <c r="E38" s="17"/>
+      <c r="F38" s="17"/>
+      <c r="G38" s="15"/>
+    </row>
+    <row r="39" spans="3:7" ht="49" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C39" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="D39" s="10" t="s">
+      <c r="D39" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="E39" s="23"/>
-      <c r="F39" s="23"/>
-      <c r="G39" s="24"/>
-    </row>
-    <row r="40" spans="3:7" ht="36" customHeight="1">
+      <c r="E39" s="17"/>
+      <c r="F39" s="17"/>
+      <c r="G39" s="15"/>
+    </row>
+    <row r="40" spans="3:7" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C40" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="D40" s="10" t="s">
+      <c r="D40" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="E40" s="23"/>
-      <c r="F40" s="23"/>
-      <c r="G40" s="24"/>
-    </row>
-    <row r="41" spans="3:7" ht="24" customHeight="1">
+      <c r="E40" s="17"/>
+      <c r="F40" s="17"/>
+      <c r="G40" s="15"/>
+    </row>
+    <row r="41" spans="3:7" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C41" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="D41" s="10" t="s">
+      <c r="D41" s="22" t="s">
         <v>132</v>
       </c>
-      <c r="E41" s="23"/>
-      <c r="F41" s="23"/>
-      <c r="G41" s="24"/>
-    </row>
-    <row r="42" spans="3:7">
-      <c r="C42" s="18"/>
+      <c r="E41" s="17"/>
+      <c r="F41" s="17"/>
+      <c r="G41" s="15"/>
+    </row>
+    <row r="42" spans="3:7" x14ac:dyDescent="0.35">
+      <c r="C42" s="6"/>
       <c r="D42" s="19"/>
       <c r="E42" s="19"/>
       <c r="F42" s="19"/>
       <c r="G42" s="19"/>
     </row>
-    <row r="43" spans="3:7">
-      <c r="C43" s="15" t="s">
+    <row r="43" spans="3:7" x14ac:dyDescent="0.35">
+      <c r="C43" s="30" t="s">
         <v>133</v>
       </c>
-      <c r="D43" s="23"/>
-      <c r="E43" s="23"/>
-      <c r="F43" s="23"/>
-      <c r="G43" s="24"/>
-    </row>
-    <row r="44" spans="3:7" ht="21.95" customHeight="1">
-      <c r="C44" s="12" t="s">
+      <c r="D43" s="17"/>
+      <c r="E43" s="17"/>
+      <c r="F43" s="17"/>
+      <c r="G43" s="15"/>
+    </row>
+    <row r="44" spans="3:7" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C44" s="31" t="s">
         <v>134</v>
       </c>
-      <c r="D44" s="24"/>
-      <c r="E44" s="10" t="s">
+      <c r="D44" s="15"/>
+      <c r="E44" s="22" t="s">
         <v>135</v>
       </c>
-      <c r="F44" s="23"/>
-      <c r="G44" s="24"/>
-    </row>
-    <row r="45" spans="3:7" ht="33.950000000000003" customHeight="1">
-      <c r="C45" s="12" t="s">
+      <c r="F44" s="17"/>
+      <c r="G44" s="15"/>
+    </row>
+    <row r="45" spans="3:7" ht="34" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C45" s="31" t="s">
         <v>136</v>
       </c>
-      <c r="D45" s="24"/>
-      <c r="E45" s="10" t="s">
+      <c r="D45" s="15"/>
+      <c r="E45" s="22" t="s">
         <v>137</v>
       </c>
-      <c r="F45" s="23"/>
-      <c r="G45" s="24"/>
-    </row>
-    <row r="46" spans="3:7" ht="21.95" customHeight="1">
-      <c r="C46" s="12" t="s">
+      <c r="F45" s="17"/>
+      <c r="G45" s="15"/>
+    </row>
+    <row r="46" spans="3:7" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C46" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="D46" s="24"/>
-      <c r="E46" s="10" t="s">
+      <c r="D46" s="15"/>
+      <c r="E46" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="F46" s="23"/>
-      <c r="G46" s="24"/>
-    </row>
-    <row r="47" spans="3:7" ht="33.950000000000003" customHeight="1">
-      <c r="C47" s="12" t="s">
+      <c r="F46" s="17"/>
+      <c r="G46" s="15"/>
+    </row>
+    <row r="47" spans="3:7" ht="34" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C47" s="31" t="s">
         <v>139</v>
       </c>
-      <c r="D47" s="24"/>
-      <c r="E47" s="10" t="s">
+      <c r="D47" s="15"/>
+      <c r="E47" s="22" t="s">
         <v>140</v>
       </c>
-      <c r="F47" s="23"/>
-      <c r="G47" s="24"/>
-    </row>
-    <row r="48" spans="3:7" ht="33.950000000000003" customHeight="1">
-      <c r="C48" s="12" t="s">
+      <c r="F47" s="17"/>
+      <c r="G47" s="15"/>
+    </row>
+    <row r="48" spans="3:7" ht="34" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C48" s="31" t="s">
         <v>141</v>
       </c>
-      <c r="D48" s="24"/>
-      <c r="E48" s="10" t="s">
+      <c r="D48" s="15"/>
+      <c r="E48" s="22" t="s">
         <v>142</v>
       </c>
-      <c r="F48" s="23"/>
-      <c r="G48" s="24"/>
-    </row>
-    <row r="49" spans="3:7" ht="45.95" customHeight="1">
-      <c r="C49" s="12" t="s">
+      <c r="F48" s="17"/>
+      <c r="G48" s="15"/>
+    </row>
+    <row r="49" spans="3:7" ht="46" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C49" s="31" t="s">
         <v>106</v>
       </c>
-      <c r="D49" s="24"/>
-      <c r="E49" s="10" t="s">
+      <c r="D49" s="15"/>
+      <c r="E49" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="F49" s="23"/>
-      <c r="G49" s="24"/>
-    </row>
-    <row r="50" spans="3:7" ht="24" customHeight="1">
-      <c r="C50" s="13" t="s">
+      <c r="F49" s="17"/>
+      <c r="G49" s="15"/>
+    </row>
+    <row r="50" spans="3:7" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C50" s="34" t="s">
         <v>144</v>
       </c>
-      <c r="D50" s="23"/>
-      <c r="E50" s="23"/>
-      <c r="F50" s="23"/>
-      <c r="G50" s="24"/>
+      <c r="D50" s="17"/>
+      <c r="E50" s="17"/>
+      <c r="F50" s="17"/>
+      <c r="G50" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="E47:G47"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="D41:G41"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="E48:G48"/>
-    <mergeCell ref="E44:G44"/>
-    <mergeCell ref="C3:G3"/>
     <mergeCell ref="C50:G50"/>
     <mergeCell ref="C44:D44"/>
     <mergeCell ref="D34:G34"/>
@@ -2388,8 +2480,18 @@
     <mergeCell ref="D35:G35"/>
     <mergeCell ref="E45:G45"/>
     <mergeCell ref="D39:G39"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="E47:G47"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="D41:G41"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="E48:G48"/>
+    <mergeCell ref="E44:G44"/>
+    <mergeCell ref="C3:G3"/>
     <mergeCell ref="C5:G5"/>
-    <mergeCell ref="C45:D45"/>
     <mergeCell ref="D42:G42"/>
     <mergeCell ref="D38:G38"/>
   </mergeCells>
